--- a/docs/downloads/04/tbl_cm_educ_sex_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -443,12 +443,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,12 +460,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -532,7 +520,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D8">
@@ -624,14 +612,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13">
@@ -642,19 +630,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -670,14 +658,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D14">
-        <v>33</v>
+        <v>237</v>
       </c>
       <c r="E14">
-        <v>8.300000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +681,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D15">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="E15">
-        <v>59.7</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16">
@@ -716,60 +704,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D16">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>30</v>
-      </c>
-      <c r="E17">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_sex_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_sex_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -417,14 +411,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>68.2</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -440,8 +428,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>68.2</v>
       </c>
     </row>
     <row r="5">
@@ -452,12 +446,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
     </row>
@@ -474,14 +468,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>40</v>
-      </c>
-      <c r="E6">
-        <v>58.8</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -497,14 +485,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>26.5</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="8">
@@ -520,37 +508,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>8.800000000000001</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>16.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -566,14 +554,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>70</v>
-      </c>
-      <c r="E10">
-        <v>63.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -589,14 +571,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
@@ -612,14 +594,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E12">
-        <v>4.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
@@ -630,19 +612,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E13">
-        <v>8.300000000000001</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14">
@@ -653,19 +635,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
-        <v>237</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>59.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
@@ -681,14 +663,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D15">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>23.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -704,13 +686,82 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>237</v>
+      </c>
+      <c r="E17">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>92</v>
+      </c>
+      <c r="E18">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="D16">
+      <c r="D19">
         <v>35</v>
       </c>
-      <c r="E16">
+      <c r="E19">
         <v>8.800000000000001</v>
       </c>
     </row>
